--- a/backend/uploads/seo_update.xlsx
+++ b/backend/uploads/seo_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://publicisgroupe-my.sharepoint.com/personal/bavkumar_publicisgroupe_net/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{ACE72C92-4B23-43DE-9DB6-DD0FBF81F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA3F32A-EB65-451C-BD21-CC79E2B94E04}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{ACE72C92-4B23-43DE-9DB6-DD0FBF81F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A3F247-7878-4C62-B144-858061B3EA08}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{811A0CCE-B5F1-4067-AED7-02300A1D97AA}"/>
   </bookViews>
@@ -41,34 +41,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>jcr:title</t>
-  </si>
-  <si>
-    <t>/content/we-retail/ca/en/men/jcr:content</t>
-  </si>
-  <si>
-    <t>Page Properties Path</t>
-  </si>
-  <si>
-    <t>jcr:description</t>
-  </si>
-  <si>
-    <t>pageTitle</t>
-  </si>
-  <si>
-    <t>cq:canonicalUrl</t>
-  </si>
-  <si>
-    <t>Meta title</t>
-  </si>
-  <si>
-    <t>meta description</t>
-  </si>
-  <si>
-    <t>Sample page</t>
-  </si>
-  <si>
-    <t>http://localhost:8080/content/we-retail/ca/en/men.html</t>
+    <t>Page Path</t>
+  </si>
+  <si>
+    <t>Meta Title</t>
+  </si>
+  <si>
+    <t>Meta Description</t>
+  </si>
+  <si>
+    <t>Page Title</t>
+  </si>
+  <si>
+    <t>Canonical URL</t>
+  </si>
+  <si>
+    <t>/content/we-retail/ca/en/men</t>
+  </si>
+  <si>
+    <t>2027 Ram 1500 TRX SRT Title</t>
+  </si>
+  <si>
+    <t>This is the new meta description</t>
+  </si>
+  <si>
+    <t>Summer Collection</t>
+  </si>
+  <si>
+    <t>https://www.ramtrucks.com/2027/ram-1500/trx.html</t>
   </si>
 </sst>
 </file>
@@ -483,24 +483,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
